--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_isapre_a_2024_antofagasta.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_isapre_a_2024_antofagasta.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 15:01</t>
+    <t xml:space="preserve">2026-09-24 01:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -970,13 +970,13 @@
         <v>9</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.27</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.07</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="20">
@@ -993,13 +993,13 @@
         <v>9</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.21</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="21">
@@ -1016,13 +1016,13 @@
         <v>9</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.19</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="22">
@@ -1085,13 +1085,13 @@
         <v>9</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-0.13</v>
+        <v>-0.08</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-0.09</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="25">
@@ -1108,13 +1108,13 @@
         <v>9</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.07</v>
+        <v>0.04</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>-0.58</v>
+        <v>-0.56</v>
       </c>
     </row>
     <row r="26">
@@ -1134,7 +1134,7 @@
         <v>-0.33</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>-0.51</v>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_isapre_a_2024_antofagasta.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_isapre_a_2024_antofagasta.xlsx
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:50</t>
+    <t xml:space="preserve">2026-10-01 23:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_isapre_a_2024_antofagasta.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_isapre_a_2024_antofagasta.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:05</t>
+    <t xml:space="preserve">2026-10-05 20:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
